--- a/docs/ai/LLM_API_비교표.xlsx
+++ b/docs/ai/LLM_API_비교표.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="호출 테스트 결과" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선정 결과" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10건 대조" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v2 대조" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v3 대조" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프롬프트 v1~v3 비교" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2012,4 +2015,2358 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>응답 시간(초)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AI 요약 (프롬프트 v2)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>6번 정답</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>올해 9월 전학 온 중학생 내담자는 새 학급에 말을 걸 친구가 없고 쉬는 시간에 혼자 앉아 있는 것이 가장 힘들며, 점심시간에 급식실을 피하고 모둠 활동이 있는 날에는 아침부터 배가 아프다고 호소함. 어머니는 아이의 말수가 줄고 방에 있는 시간이 늘었다고 걱정하였으나 수면과 식사는 큰 변화가 없다고 보고함.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>전학 후 새 학급에서 친구가 없어 학교 가기를 싫어하며, 모둠 활동이 있는 날 아침에 복통을 호소함.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>정답보다 상세하지만 모두 원본에 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>자해나 자살과 관련된 언급은 없었으며 이에 대해 직접 확인함. 상담 목표는 학교에서 편하게 있을 수 있는 시간 만들기로 함께 정함.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>상담 목표를 학교에서 편하게 있을 수 있는 시간 만들기로 정하고, 자해·자살 관련 언급 여부를 직접 확인함(언급 없음).</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>v1의 '청취하였고' 삭제, 상담 목표 설정 포함 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기까지 하루 중 덜 불편했던 순간을 한 번씩 적어 오기로 함.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기까지 하루 중 덜 불편했던 순간을 한 번씩 적어 오기.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>v1의 항목 오분류 해결 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>인사말을 옆자리 친구에게 두 번 써 보았고 한 번 대답을 들었다고 함. 아침 복통은 주 1회로 줄었으며 점심시간에 급식실에 갔다고 보고함.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>정답은 '기록에 없음'. 보고 내용을 호소로 썼지만 원본에 있는 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>v1의 지어낸 '확인하였다'를 '기록에 없음'으로 고침 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에는 동아리나 방과후 활동 중 관심 있는 것을 함께 찾아보기로 함.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에 동아리나 방과후 활동 중 관심 있는 것을 함께 찾아보기.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>방과후 활동 후보인 미술, 독서, 코딩 중 미술에 관심을 보였으며, 점심시간 2회 중 1회 동급생과 같이 앉았다고 함. 최근 2주간 복통 호소가 없었고, 어머니에 따르면 집에서 말수가 조금 늘었다고 함.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>점심시간 2회 중 1회 동급생과 같이 앉았고, 복통 호소가 최근 2주간 없는 등 호전된 모습을 보고함.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>v1의 '관찰됨' 삭제 → 개선. 방과후 후보를 호소 칸에 넣음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>위기 신호가 없음을 확인하고, 담임교사에게 방과후 신청 안내를 요청하는 것에 내담자가 동의함을 확인함.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>방과후 활동 후보(미술, 독서, 코딩)를 이야기하고, 담임교사에게 방과후 신청 안내를 요청하는 것에 대한 내담자 동의를 확인함. 위기 신호 없음.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>'위기 신호 없음'은 포함. 방과후 후보 논의는 호소 칸으로 감</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>방과후 미술 첫 참여 후 소감 이야기하기.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>방과후 미술 첫 참여 후 소감 이야기하기.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>친한 친구 무리와 멀어져 혼자 있게 되었고, 단체 대화방 오해로 연락이 줄어 속상하며 교실에서 눈치를 보게 됨. 잠드는 데 1시간 이상 걸리는 수면 문제(주 3~4회)와 학업 집중 저하가 있고, 친구들과 다시 이야기할 방법을 알고 싶어 함.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>친한 친구 무리와 멀어져 혼자 있게 되었고, 교실에서 눈치를 보며 잠드는 데 1시간 이상 걸리는 날이 주 3~4회이고 집중이 잘 안 됨.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>수면, 집중, 기대까지 포함 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>자해·자살 관련 언급이 없는지 직접 확인하였으며, 초기 질문지 작성 완료 및 개인정보 수집 동의를 받음.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>접수 상담으로 초기 질문지 작성과 개인정보 수집 동의를 받고, 자해·자살 관련 언급 여부를 직접 확인함(언급 없음).</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정 후 1회기 일정 안내. 보호자 동의 서류 다음 방문 시 지참 안내.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정 후 1회기 일정 안내, 다음 방문 시 보호자 동의 서류 지참.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>공고 6개를 읽고 서비스 기획 직무에 가장 흥미를 느낌. 요구 역량 중 포트폴리오가 없어 부담을 호소함.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>서비스 기획 직무에 가장 흥미를 느끼나 포트폴리오가 없어 부담을 호소함.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>읽어 온 채용 공고 6개의 결과를 확인함.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>정답 재검토</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>v1과 같이 '기록에 없음'. 정답의 '확인함'이 추정일 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>소규모 포트폴리오 목표 정하기.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>소규모 포트폴리오 목표 정하기.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>불안한 생각 기록 6건 중 대부분 업무 실수에 대한 걱정이었고 실제로 실수가 있었던 적은 1건이었음. 수면은 많이 나아졌으나 새벽에 깨는 날이 주 1회 남아 있다고 함.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>업무 실수에 대한 걱정이 대부분이며, 새벽에 깨는 날이 주 1회 남아 있음.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>불안한 생각 기록 6건을 함께 살펴보고, 걱정이 실제 사건으로 이어진 정도를 확인하며 내담자가 스스로 과장된 부분을 찾아내었음. 2주 후에도 새벽 각성이 이어지면 의료기관 상담을 고려하기로 합의함.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>불안한 생각 기록 6건을 함께 검토해 실제 실수가 1건뿐임을 확인했고, 내담자가 과장된 부분을 스스로 찾아냄.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>항목 오분류</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>'2주 후 새벽 각성 지속 시 의료기관 상담 고려' 합의가 개입 칸으로 감 (새로 생긴 문제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에 하루 활동 목록을 점검하기로 함.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에 하루 활동 목록을 점검하고, 2주 후에도 새벽 각성이 이어지면 의료기관 상담을 고려하기로 합의함.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>의료기관 상담 고려 합의가 계획 칸에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>역할 분담표를 만들어 주 2일 배우자가 숙제를 지도하기로 하였고, 지난 3주간 큰 다툼은 한 번이었으나 타임아웃 규칙으로 빠르게 가라앉았다고 보고함. 아이의 표정이 밝아졌고 지금은 스스로 조절할 수 있을 것 같다는 자신감을 표현함.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>초기 호소였던 잦은 갈등이 줄어 상담 목표가 달성됨.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>결과(갈등 감소 등)를 호소 칸에 넣음. 원본에 있는 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>갈등 상황별로 쓸 수 있는 대응 방법을 함께 복습함. 초기 호소였던 잦은 갈등이 줄고 상담 목표가 달성되었다고 상호 확인하였으며, 내담자의 종결 희망과 상담자 평가가 일치하여 본 회기를 마지막으로 종결하기로 함.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>배우자와 만든 역할 분담표와 타임아웃 규칙의 사용 경과를 확인하고, 갈등 상황별 대응 방법을 복습함. 재신청이 가능함을 안내함.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>항목 오분류</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>종결 결정이 개입 칸에만 들어감 (새로 생긴 문제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>어려움이 다시 커질 때 재신청이 가능함을 안내하였고, 사후 점검은 필요 시 내담자가 요청하는 방식으로 안내함.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>본 회기를 마지막으로 종결(종결 사유: 목표 달성). 사후 점검은 내담자가 요청할 때 진행.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>종결 결정이 계획 칸에 없음. 재신청·사후 점검 안내는 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>서류 준비 완료를 확인하고, 본 기관 상담 범위를 넘는 신청·심사 업무는 지역 복지 담당 부서 소관임을 안내함. 내담자 동의 후 필요한 정보만 가상 복지 지원과로 연계 의뢰서 작성하여 전달함. 정서 지지 상담은 필요 시 재개 가능하다고 안내함.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>신청·심사 업무가 지역 복지 담당 부서 소관이라 연계 의뢰서를 작성하고, 내담자 동의 후 필요한 정보만 전달함. 정서 지지 상담은 필요 시 재개 가능함을 안내함.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>원본에 없는 표현</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>'소관임을 안내함'은 원본에 없는 표현 (경미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>연계 후 1주 내 진행 상황 확인 전화를 할 예정임.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>연계 후 1주 내 진행 상황 확인 전화를 하기로 함. 사례 상태를 연계로 전환.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>'사례 상태 연계로 전환' 빠짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>대학 취업지원센터 소개로 진로 고민을 호소함.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>진로 고민 (대학 취업지원센터 소개로 신청).</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>v1의 '내원하여' 삭제 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>초기 질문지·동의서 작성 완료, 위기 신호 없음.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>접수 상담으로 초기 질문지와 동의서 작성을 완료하고 위기 신호가 없음을 확인함.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>접수 종료, 담당 상담자 배정 후 1회기 일정 안내.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정 후 1회기 일정 안내.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>v1의 항목 오분류 해결 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>학교 적응 관련 어려움이 줄었다고 보고함.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>학교 적응 관련 어려움이 줄었다고 보고함. 취침이 늦어지는 날이 주 3일에서 주 1일로 줄어듦.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>v1의 지어낸 '지원이 필요한 상태' 삭제 → 개선. 취침 감소 정보는 빠짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>수학 질문 시도 결과를 확인하고 학습 지원 프로그램(주 2회)을 신청함. 평일 하루 1과목 복습하는 주간 학습 계획표를 작성함.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>잘못된 '기록에 없음'</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>원본에 수학 질문, 학습 지원 프로그램 신청, 주간 학습 계획표 작성이 있는데 '기록에 없음'이라고 함 (v2에서 새로 생긴 오류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>계획 실행 점검 및 종결 여부 이야기.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>계획 실행 점검과 종결 여부 이야기.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>응답 시간(초)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AI 요약 (프롬프트 v3)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>6번 정답</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>올해 9월 전학을 온 중학생 내담자가 학교에 가기 싫어하며, 새 학급에 말을 걸 친구가 없고 쉬는 시간에 혼자 앉아 있는 것이 힘들다고 함. 점심시간에 급식실 가는 것을 피하고 모둠 활동이 있는 날에는 아침부터 배가 아프며, 어머니는 아이의 말수가 줄고 방에 있는 시간이 늘었다고 걱정함.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>전학 후 새 학급에서 친구가 없어 학교 가기를 싫어하며, 모둠 활동이 있는 날 아침에 복통을 호소함.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>자해나 자살과 관련된 언급은 없었으며 이에 대해 직접 확인하였고, 학교에서 편하게 있을 수 있는 시간 만들기를 상담 목표로 함께 정함.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>상담 목표를 학교에서 편하게 있을 수 있는 시간 만들기로 정하고, 자해·자살 관련 언급 여부를 직접 확인함(언급 없음).</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SE01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기까지 하루 중 덜 불편했던 순간을 한 번씩 적어 오기로 함.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기까지 하루 중 덜 불편했던 순간을 한 번씩 적어 오기.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>인사말을 옆자리 친구에게 두 번 써 보고 한 번은 대답을 들었다고 함. 아침 복통은 주 1회로 줄었으며 점심시간에 급식실에 갔다고 보고함.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>정답은 '기록에 없음'. 원본에 있는 보고 내용을 호소로 씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SE03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>동아리나 방과후 활동 중 관심 있는 것을 함께 찾아보기로 함.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에 동아리나 방과후 활동 중 관심 있는 것을 함께 찾아보기.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>방과후 활동 후보(미술, 독서, 코딩) 중 미술에 관심을 보임. 점심시간 2회 중 1회 동급생과 같이 앉음. 복통 호소 최근 2주간 없음. 어머니 f/u: 집에서 말수 조금 늘었다고 함. 위기 신호 없음.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>점심시간 2회 중 1회 동급생과 같이 앉았고, 복통 호소가 최근 2주간 없는 등 호전된 모습을 보고함.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>항목 오분류</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>'위기 신호 없음'이 호소 칸에 들어감 (규칙 6은 개입 칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>담임교사에게 방과후 신청 안내를 요청하는 것에 내담자 동의를 확인함.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>방과후 활동 후보(미술, 독서, 코딩)를 이야기하고, 담임교사에게 방과후 신청 안내를 요청하는 것에 대한 내담자 동의를 확인함. 위기 신호 없음.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>위기 신호 없음, 방과후 후보 논의가 개입 칸에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SE04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>방과후 미술 첫 참여 후 소감 이야기하기.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>방과후 미술 첫 참여 후 소감 이야기하기.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>학교 상담교사 소개로 본인이 신청하였으며, 친한 친구 무리와 멀어져 혼자 있게 되고 단체 대화방의 오해로 연락이 줄어 속상함과 교실 눈치를 보고 있음. 잠드는 데 1시간 이상 걸리고 주 3~4회 발생하며 학업 집중이 잘 안 된다고 호소함.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>친한 친구 무리와 멀어져 혼자 있게 되었고, 교실에서 눈치를 보며 잠드는 데 1시간 이상 걸리는 날이 주 3~4회이고 집중이 잘 안 됨.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>자해·자살 관련 언급이 없음을 직접 확인함. 초기 질문지 작성을 완료하고 개인정보 수집 동의를 받음. 담당 상담자 배정 후 1회기 일정을 안내하고, 보호자 동의 서류를 다음 방문 시 지참하도록 안내함.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>접수 상담으로 초기 질문지 작성과 개인정보 수집 동의를 받고, 자해·자살 관련 언급 여부를 직접 확인함(언급 없음).</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>일정 안내, 서류 안내도 개입 칸에 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SE05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정에 따른 1회기 진행 및 보호자 동의 서류 지참.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정 후 1회기 일정 안내, 다음 방문 시 보호자 동의 서류 지참.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>'1회기 일정 안내'가 '1회기 진행'으로 바뀜 (경미)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>공고 6개를 읽고 서비스 기획 직무에 가장 흥미를 느낌. 요구 역량 중 포트폴리오가 없어 부담을 호소함.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>서비스 기획 직무에 가장 흥미를 느끼나 포트폴리오가 없어 부담을 호소함.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>읽어 온 채용 공고 6개의 결과를 확인함.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>정답 재검토</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>'기록에 없음'. 정답의 '확인함'이 추정일 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SE08</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>소규모 포트폴리오 목표 정하기.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>소규모 포트폴리오 목표 정하기.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>불안한 생각 기록 6건을 살펴보았으며, 대부분 업무 실수에 대한 걱정이었고 실제로 실수가 있었던 적은 1건이었음. 수면은 많이 나아졌으나 새벽에 깨는 날이 주 1회 남아 있다고 보고함.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>업무 실수에 대한 걱정이 대부분이며, 새벽에 깨는 날이 주 1회 남아 있음.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>걱정이 실제 사건으로 이어진 정도를 확인하며 내담자가 스스로 과장된 부분을 찾아내었음. 2주 후에도 새벽 각성이 이어지면 의료기관 상담을 고려하기로 합의함.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>불안한 생각 기록 6건을 함께 검토해 실제 실수가 1건뿐임을 확인했고, 내담자가 과장된 부분을 스스로 찾아냄.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>합의 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SE13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2주 후에도 새벽 각성이 이어지면 의료기관 상담을 고려하기로 합의함. 다음 회기에 하루 활동 목록을 점검하기로 함.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>다음 회기에 하루 활동 목록을 점검하고, 2주 후에도 새벽 각성이 이어지면 의료기관 상담을 고려하기로 합의함.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>v2의 누락 해결 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>역할 분담표를 배우자와 함께 만들어 오고 주 2일은 배우자가 숙제를 지도하기로 함. 지난 3주간 큰 다툼은 한 번이었으나 타임아웃 규칙을 써서 빠르게 가라앉았고 아이도 최근 표정이 밝아짐. 갈등이 줄어들어 지금은 스스로 조절할 수 있을 것 같다는 자신감을 표현함.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>초기 호소였던 잦은 갈등이 줄어 상담 목표가 달성됨.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>결과(갈등 감소 등)를 호소 칸에 넣음. 원본에 있는 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>갈등 상황별로 쓸 수 있는 대응 방법을 함께 복습함. 어려움이 다시 커질 때 재신청이 가능함을 안내함. 초기 호소였던 잦은 갈등이 줄고 상담 목표가 달성되었다고 상호 확인하였으며, 내담자의 종결 희망과 상담자 평가가 일치하여 본 회기를 마지막으로 종결하기로 합의함.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>배우자와 만든 역할 분담표와 타임아웃 규칙의 사용 경과를 확인하고, 갈등 상황별 대응 방법을 복습함. 재신청이 가능함을 안내함.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>종결 결정 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SE17</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>본 회기를 마지막으로 종결함(종결 사유: 목표 달성). 사후 점검은 필요 시 내담자가 요청하는 방식으로 안내함.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>본 회기를 마지막으로 종결(종결 사유: 목표 달성). 사후 점검은 내담자가 요청할 때 진행.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>v2의 누락 해결 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>기록에 없음</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>서류 준비 완료를 확인하고, 본 기관 상담 범위를 넘는 신청 및 심사 업무는 지역 복지 담당 부서 소관임을 안내함. 가상 복지 지원과 연계를 위한 의뢰서를 작성하고, 내담자의 동의 후 필요한 정보만 전달함. 정서 지지 상담은 필요 시 재개 가능함을 안내함.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>신청·심사 업무가 지역 복지 담당 부서 소관이라 연계 의뢰서를 작성하고, 내담자 동의 후 필요한 정보만 전달함. 정서 지지 상담은 필요 시 재개 가능함을 안내함.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>원본에 없는 표현</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>'소관임을 안내함'은 원본에 없는 표현 (경미, v2와 같음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SE20</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>가상 복지 지원과로 연계하고, 연계 후 1주 내 진행 상황 확인 전화를 하기로 함. 사례 상태를 연계로 전환함.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>연계 후 1주 내 진행 상황 확인 전화를 하기로 함. 사례 상태를 연계로 전환.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>사례 상태 전환 포함 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>대학 취업지원센터 소개로 진로 고민을 호소함.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>진로 고민 (대학 취업지원센터 소개로 신청).</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>초기 질문지와 동의서 작성을 완료하고, 위기 신호가 없음을 확인함.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>접수 상담으로 초기 질문지와 동의서 작성을 완료하고 위기 신호가 없음을 확인함.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SE32</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>접수 종료 후 담당 상담자를 배정하고 1회기 일정을 안내함.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>담당 상담자 배정 후 1회기 일정 안내.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>주요 호소</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>학교 적응 관련 어려움이 줄었다고 보고함. 취침 시간이 늦어지는 날이 주 3일에서 주 1일로 감소함.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>학교 적응 관련 어려움이 줄었다고 보고함. 취침이 늦어지는 날이 주 3일에서 주 1일로 줄어듦.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>취침 감소 포함 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>개입 내용</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>수학 질문 1회를 시도하고 선생님이 친절히 답해 줌. 학습 지원 프로그램을 신청함(주 2회). 주간 학습 계획표를 작성하여 평일 하루 1과목 복습하기로 함.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>수학 질문 시도 결과를 확인하고 학습 지원 프로그램(주 2회)을 신청함. 평일 하루 1과목 복습하는 주간 학습 계획표를 작성함.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>v2의 잘못된 '기록에 없음' 해결 → 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SE35</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>다음 계획</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>계획 실행 점검 및 종결 여부 이야기.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>계획 실행 점검과 종결 여부 이야기.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>v1 (칸 수)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>v2 (칸 수)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>v3 (칸 수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>일부 누락</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>원본에 없는 표현</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>항목 오분류</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>표현 차이</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>정답 재검토</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>잘못된 '기록에 없음'</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>평균 응답 시간(초)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>JSON·필드 정상</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>해석</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>v3는 일치 23칸(77%)으로 가장 좋다. v2에서 생긴 SE35 개입 오류와 SE13·SE17 누락을 고쳤다. 남은 문제는 SE04의 위기 신호 칸 배치, SE20의 '안내함' 표현 정도이다. 응답 시간은 서버 상태에 따라 달라져 프롬프트 효과로 보지 않는다.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>